--- a/data/nyc_construction_leads.xlsx
+++ b/data/nyc_construction_leads.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>40-38 189 STREET, Queens</t>
+          <t>211-07 34 ROAD, Queens</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -503,16 +503,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4038 EASTERN REALTY LLC</t>
+          <t>211-05 34TH RD REALTY LLC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -521,22 +521,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Q01466083-I1</t>
+          <t>Q01403320-S4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PROPOSE A NEW TWO STORY WITH TWO FAMILY HOUSE. OBTAIN NEW C OF O.</t>
+          <t>FILE PL &amp; SP WORKTYPE IN CONJUNCTION WITH JOB#Q01403320</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>XIAOHONG</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ZHAO</t>
+          <t>HUANG</t>
         </is>
       </c>
     </row>
@@ -551,17 +551,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8-48 ASTORIA BOULEVARD, Queens</t>
+          <t>14 DOE PLACE, Staten Island</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MR. OLU COLE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -579,22 +579,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Q01450056-S4</t>
+          <t>S00965093-S6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MECHNICAL SYSTEM FOR NEW 7-STORY MONOLITHIC CONCRETE BUILDING</t>
+          <t>Installation of a 9' curb cut (6' cc with (2) 18" splays)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>LALITH</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sorokko</t>
+          <t>RAJAKARUNA</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1663 EAST   18 STREET, Brooklyn</t>
+          <t>26-37 30 STREET, Queens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>30th Street Property Holdings LLC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -637,22 +637,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B01405960-S3</t>
+          <t>Q01385871-S2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>INSTALL NEW MECHANICAL SYSTEM THROUGHOUT NEW 12-STORY MONOLITHIC CONCRETE BUILDING</t>
+          <t>INSTALLATION OF PLUMBING SYSTEM FOR ENTIRE BUILDING INCONJUNCTION WITH NB JOB #Q01385871-I1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Dmitry</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sorokko</t>
+          <t>Levin</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>144 WILD AVENUE, Staten Island</t>
+          <t>8741 BAY   16 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>S01371873-I1</t>
+          <t>B01463420-I1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CONSTRUCT A TWO FAMILY RESIDENCE WITH ACCESSORY OFF-STREET PARKING FOR TWO CARS</t>
+          <t>PROPOSE A NEW THREE STORY WITH THREE FAMILY DWELLINGS FAMILY.  OBTAIN NEW C OF O.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>XIAOHONG</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Krebushevski</t>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40-38 189 STREET, Queens</t>
+          <t>211-03 34 ROAD, Queens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -735,16 +735,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4038 EASTERN REALTY LLC</t>
+          <t>211-05 34TH RD REALTY LLC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,217 +753,221 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Q01466083-S1</t>
+          <t>Q01403318-S4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FILE SOE IN CONJUNCTION WITH JOB#Q01466083</t>
+          <t>FILE PL &amp; SP WORKTYPE IN CONJUNCTION WITH JOB#Q01403318</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>XIAOHONG</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ZHAO</t>
+          <t>HUANG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>783 QUINCY STREET, Brooklyn</t>
+          <t>211-05 34 ROAD, Queens</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>211-05 34TH RD REALTY LLC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>B01464808-I1</t>
+          <t>Q01404099-S4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Repair of damaged brownstone and peeling plaster/paint on Exposure 1 facade</t>
+          <t>FILE PL &amp; SP WORKTYPE IN CONJUNCTION WITH JOB#Q01404099</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sunil</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Saigal</t>
+          <t>HUANG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>200 WEST   57 STREET, Manhattan</t>
+          <t>2124 AVENUE P, Brooklyn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Feil Organization</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>M01463256-S2</t>
+          <t>B01381870-S7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IOR ALTERATION WITHIN EXISTING TENANT SPACE STE 708 ON 7TH FLOOR IN EXISTING BUILDING: NEW PLUMBING FIXTURES PER NEW LAYOUT, NEW DENTAL PLUMBING FIXTURES PER DENTAL NEEDS, NEW ELECTRICAL HOT WATER HEATER, NO CHANGE TO OCCUPANCY, GROUP AND USE.</t>
+          <t>STRUCTURAL WORKS FOR NEW 12-STORY MONOLITHIC CONCRETE BUILDING</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>XIU</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>Sorokko</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31-40 35 STREET, Queens</t>
+          <t>8743 BAY   16 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Queens</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Q01462560-I1</t>
+          <t>B01463830-I1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>INTERIOR RENOVATION OF EXISTING RESIDENTIAL APARTMENT TO UPDATE BEDROOM LAYOUT. NEW WALLS AND OUTLETS PER PLAN. NO CHANGE IN EGRESS, USE OR OCCUPANCY.</t>
+          <t>PROPOSE A NEW THREE STORY WITH THREE FAMILY DWELLING HOUSE. OBTAIN NEW C OF O.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kun</t>
+          <t>XIAOHONG</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>200 WEST   57 STREET, Manhattan</t>
+          <t>8745 BAY   16 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Feil Organization</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,31 +976,31 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M01463256-S1</t>
+          <t>B01463422-I1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>INTERIOR ALTERATION WITHIN EXISTING TENANT SPACE STE 708 ON 7TH FLOOR IN EXISTING BUILDING: NEW VRF SYSTEM WITH ROOFTOP CONDENSER AND INDOOR AIR HANDLERS NEW FRESH AIR INTAKE SYSTEM NEW EXHAUST FAN SYSTEM NEW ASSOCIATED DUCTWORK, DIFFUSERS, AND PIPING.</t>
+          <t>PROPOSE A NEW THREE STORY WITH THREE FAMILY DWELLINGS HOUSE. OBTAIN NEW C OF O.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>XIU</t>
+          <t>XIAOHONG</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
@@ -1011,50 +1015,50 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>262 5 AVENUE, Manhattan</t>
+          <t>165 RUTLAND ROAD, Brooklyn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Doria Scaffolding LLC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>M01330105-S2</t>
+          <t>B01457959-I1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY MATERIAL HOIST ON OUTRIGGERS PER PLAN SUBMITTED. WORK SHALL COMPLY WITH 2022 BUILDING CODE CHAPTER 33. NO CHANGE IN USE, EGRESS AND/OR OCCUPANCY WITH THIS APPLICATION.</t>
+          <t>APPLICATION FILE TO EXTERIOR FACADE REPAIR AS RECONSTRUCTION OF THE FRONT MASONRY, STAIR, SIDE CHEEK WALLS  AND CORNICE PAINTING AT FRONT ELEVATION. REMOVE VIOLATION# 39198431L.. NO CHANGE IN USE, EGRESS OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ZELJKO</t>
+          <t>Mumtaz</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>STEVANOVIC</t>
+          <t>Hussain</t>
         </is>
       </c>
     </row>
@@ -1069,50 +1073,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14 WEST  170 STREET, Bronx</t>
+          <t>341 KINGSBOROUGH    3 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Latino Pastoral Action Center</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X01464173-I1</t>
+          <t>B01455837-I1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Removal of existing roof assembly down to existing structural metal roof deck and installation of new roof insulation and TPO roofing membrane system over existing structural metal roof deck. No change in use or occupancy. No structural work.</t>
+          <t>INSTALLATION OF TEMPORARY SIDEWALK SHED AT 341 KINGSBOROUGH 3 WALK, BROOKLYN, NY 11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Royes</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1131,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>173 CANAL STREET, Manhattan</t>
+          <t>459 EAST  149 STREET, Bronx</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RABER ENTERPRISES LLC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1146,31 +1150,31 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>M01462390-I1</t>
+          <t>X01038608-P1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1ST FLOOR INTERIOR RENOVATION. REMOVE AND INSTALL NEW PARTITIONS. NO CHANGE IN USE, OCCUPANCY, OR EGRESS UNDER THIS APPLICATION.</t>
+          <t>RENOVATE EXISTING STORES, REMOVE NON BEARING PARTITIONS AND COUNTERS</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ruoyu</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Wei</t>
+          <t>Koons</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>83-05 116 STREET, Queens</t>
+          <t>86-21 89 STREET, Queens</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1195,40 +1199,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PARKSITE CONSTRUCTION CORP</t>
+          <t>GOLDEN ROCK 2026 LLC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Q01462049-I1</t>
+          <t>Q01466154-I1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>APPLICATION FILED FOR SUPPORT-OF-EXCAVATION FOR A NEW V15-6 CON EDISON VAULT UNDER THE SIDEWALK AT 83-05 116 STREET, QUEENS, NY</t>
+          <t>INTERIOR RENOVATION OF EXISTING CELLAR TO CURE ECB VIOLATIONS# 34232266L; 34458272J. NO CHANGE IN USE, OCCUPANCY OR EGRESS.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SAMER</t>
+          <t>LOUIS</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ABOU-GHAIDA</t>
+          <t>KONG</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45 SUTTON PLACE SOUTH, Manhattan</t>
+          <t>111 BROADWAY, Manhattan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1251,38 +1255,42 @@
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CAPITAL PROPERTIES</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>M01463366-S1</t>
+          <t>M01386850-P1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>renovate kitchen, replace bathroom fixtures and install new washing machine. no change in use, egress or occupancy.</t>
+          <t>SPRINKLER MODIFICATIONS TAKING PLACE ON 20TH FLOOR AS PER PLANS FILED HEREWITH. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Helge</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Fuhrmann</t>
+          <t>Snyder</t>
         </is>
       </c>
     </row>
@@ -1297,17 +1305,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25 WASHINGTON SQUARE NORTH, Manhattan</t>
+          <t>127 KINGSBOROUGH    1 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PYRAMID RESTORATION NY</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1316,31 +1324,31 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>M01449368-I1</t>
+          <t>B01450003-I1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PROPOSED INSTALLATION OF TEMPORARY PIPE SCAFFOLD AS PER PLANS. WORK SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. NO CHANGE IN USE, OCCUPANCY, OR EGRESS UNDER THIS APPLICATION.</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 127 KINGSBOROUGH 1 WALK BROOKLYN NY 11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1363,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>663 ROGERS AVENUE, Brooklyn</t>
+          <t>171 EAST   93 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1365,40 +1373,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MICASAA</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>B01463979-I1</t>
+          <t>B01457449-S1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>APPLICATION FILING TO INSTALL CONDENSING UNIT AT ROOF TOP AS PER PLAN. NO CHANGE OF USE, EGRESS AND OCCUPANCY UNDER THIS APPLICATION.</t>
+          <t>INTERIOR RENOVATION OF CELLAR. REMOVE KITCHEN AND BATHTUB INSTALL NEW BATHRROM. FIILE TO ADDRESS ECB VIOLATION 34275318Y</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>KAMRUL</t>
+          <t>Oswin</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>AHSAN</t>
+          <t>Fairweather</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1421,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63 PENNSYLVANIA AVENUE, Brooklyn</t>
+          <t>108 KINGSBORO    1 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1423,7 +1431,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROSE SHEPHERD MANAGEMENT</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1432,31 +1440,31 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>B00656210-P2</t>
+          <t>B01450001-I1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mechanical work as shown on plans</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 108 KINGSBOROUGH 1 WALK BROOKLYN NY  11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Evodia</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1479,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>107 WEST  132 STREET, Manhattan</t>
+          <t>171 EAST   93 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1486,35 +1494,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>M01418005-S5</t>
+          <t>B01457449-I1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FRONT AND REAR FACADE RESTORATION WORK AS PER PLANS</t>
+          <t>INTERIOR RENOVATION OF CELLAR LEVEL. MINIOR PARTION WORK. REMOVE KITCHEN AND BATHTUB AND INSTALL NEW BATHROOM. FILE TO ADDRESS VIOLATION ECB 34275318Y.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>JEFFREY</t>
+          <t>Oswin</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BELL</t>
+          <t>Fairweather</t>
         </is>
       </c>
     </row>
@@ -1529,50 +1537,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>200 WEST   57 STREET, Manhattan</t>
+          <t>242 45 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The Feil Organization</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>121700</t>
+          <t>57500</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>M01463256-I1</t>
+          <t>B01459667-S1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>INTERIOR ALTERATION WITHIN EXISTING TENANT SPACE STE 708 ON 7TH FLOOR IN EXISTING BUILDING: NEW NON-BEARING INTERIOR PARTITIONS, NEW INTERIOR FINISHES, NEW MILLWORK, NEW LIGHTING. NO CHANGE TO OCCUPANCY, GROUP AND USE.</t>
+          <t>NEW KITCHEN LAYOUT ON FIRST AND SECOND FLOORS, REPLACEMENT OF BATHROOM FIXTURES, EXISTING GAS METER 1 TO CONNECT TO EXISTING BOILER WITH INDIRECT TANK AND GAS RANGE ON FIRST FLOOR ONLY. EXISTING GAS METER 2 TO BE REMOVED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>XIU</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>Lievano</t>
         </is>
       </c>
     </row>
@@ -1587,17 +1595,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>40-38 189 STREET, Queens</t>
+          <t>308 KINGSBORO    3 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4038 EASTERN REALTY LLC</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1606,31 +1614,31 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Q01466129-I1</t>
+          <t>B01452530-I1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>INSTALL 8' TEMPORARY CONSTRUCTION FENCE AT THE ABOVE ADDRESS</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 308 KINGSBOROUGH 3 WALK BROOKLYN NY 11233  AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1653,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>173 CANAL STREET, Manhattan</t>
+          <t>4137 3 AVENUE, Bronx</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RABER ENTERPRISES LLC</t>
+          <t>RBA DEVELOPERS LLC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1664,31 +1672,31 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>M01462390-S1</t>
+          <t>X01459199-I1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IST FLOOR INTERIOR RENOVATION. INSTALL PLUMBING FIXTURES. NO CHANGE IN USE, OCCUPANCY, OR EGRESS UNDER THIS APPLICATION.</t>
+          <t>Install plumbing systems in conjunction with NB X01223342-I1. There is no change in use, occupancy, or egress.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ruoyu</t>
+          <t>Gregory</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Wei</t>
+          <t>Mortman</t>
         </is>
       </c>
     </row>
@@ -1703,17 +1711,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>233 SOUTH    3 STREET, Brooklyn</t>
+          <t>1407 BROADWAY, Manhattan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GREENBROOK PARTNERS</t>
+          <t>SHORENSTEIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1722,31 +1730,31 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>172500</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B01456715-I1</t>
+          <t>M01457423-I1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Renovation to existing commercial first floor tenant space. New equipment and finishes for bakery build out. Add one door to existing storefront. Plumbing and HVAC filed subsequently</t>
+          <t>INTERIOR RENOVATIONS CONSISTING OF PARTITIONS AND FINISHES  AS PER PLANS FILED HEREWITH. NO  CHANGE TO USE, EGRESS OR OCCUPANCY</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Cortney</t>
+          <t>LEMUEL</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Walleston</t>
+          <t>GUIDOS</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1769,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6645 BROADWAY, Bronx</t>
+          <t>1311 THIERIOT AVENUE, Bronx</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1771,40 +1779,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CEDARBRIDGE</t>
+          <t>CREPAS LLC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X01462292-I1</t>
+          <t>X01462758-I1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PROPOSED TO REPAIR THE BOTTOM OF THE EXISTING STRUCTURAL FOR THE PART OF THE GARAGE AT CELLAR. REINFORCED CONCRETE SLAB,  SUPPORING THE FIRST FLOOR IN ADDITION TO CONCRETE ENCASEMENT FOR STRUCTURAL STEEL ELEMENTS. THERE IS NO CHANGE OCCUANCY, USE OR EGRES</t>
+          <t>Replace seven (7) steel window lintels facing the street and repoint facade cracks as necessary. No change in use, egress, or occupancy.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Edwin</t>
+          <t>SAHAND</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Cheuk</t>
+          <t>AINECHI</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1827,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>547 CLINTON STREET, Brooklyn</t>
+          <t>2303 AVENUE D, Brooklyn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1838,31 +1846,31 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>B01454896-P1</t>
+          <t>B01403876-P1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>LEGALIZE THE REMOVAL OF ILLEGAL SPIRAL STAIRCASE BETWEEN 1ST AND 2ND FLOOR COMBING TWO APARTMENTS.  LEGALIZE THE INSTALLATION OF FIREBOX DAMPER AT 1ST FLOOR FIREPLACE.  THIS WILL ADDRESS DOB VIOLATION VW 110298C06MJ11.</t>
+          <t>Plumbing work in conjunction with interior renovation</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>REGINALD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>THOMAS</t>
+          <t>MOSTAFA</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1885,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>45 SUTTON PLACE SOUTH, Manhattan</t>
+          <t>148 MADISON AVENUE, Manhattan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1885,38 +1893,42 @@
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GFP REAL ESTATE LLC</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>147200</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>M01463366-I1</t>
+          <t>M01399810-S2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Renovation of Apartment 3J as per plans</t>
+          <t>Installation of new split heat pump and ventilation equipment for an existing commercial space.  No change of use, egress or occupancy under this application.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Helge</t>
+          <t>Tyrone</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Fuhrmann</t>
+          <t>Wells</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1943,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3520 TILDEN AVENUE, Brooklyn</t>
+          <t>342 KINGSBORO    3 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1941,40 +1953,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>B01459311-I1</t>
+          <t>B01452518-I1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>FILING TO OBTAIN CERTIFICATE OF COMPLIANCE.  JOB PREVIOUSLY FILED UNDER JOB # B00552772-I1.  INITIAL SCOPE OF WORK WAS TO REPLACE THE CONDENSER ON THE ROOF.  NO ROPOSED WORK ON THIS APPLICATION.</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 342 KINGSBOROUGH 3 WALK  BROOKLYN NY 11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>KENNETH</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PHILOGENE</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -1989,50 +2001,50 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>118 NOEL ROAD, Queens</t>
+          <t>2675 PITKIN AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Q01465575-I1</t>
+          <t>B01330815-P1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>LIFT OF EXISTING ONE FAMILY DWELLING UNIT</t>
+          <t>INTERIOR RENOVATION OF EXISTING COMMERCIAL SPACE FOR FOOD TAKEOUT INCLUDING CARPENTRY, NEW PARTITIONS, NEW COMMERCIAL KITCHEN, EXHAUST HOOD, FAN INSTALL. NO CHANGE IN USE, OCCUPANCY AND EGRESS IS INVOLVED UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>KARTIK</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SKVIRSKY</t>
+          <t>CHANDA</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2059,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>306 SHERIDAN AVENUE, Brooklyn</t>
+          <t>584 KOSCIUSZKO STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2066,31 +2078,31 @@
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B01463073-I1</t>
+          <t>B01433221-I1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>AXMISAXJIWHD</t>
+          <t>Legalize installation of parking shed</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Mohammad</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Alauddin</t>
+          <t>ROSS</t>
         </is>
       </c>
     </row>
@@ -2105,26 +2117,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>200 WEST   57 STREET, Manhattan</t>
+          <t>207 KINGSBORO    2 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The Feil Organization</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2133,22 +2145,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>M01463256-S3</t>
+          <t>B01452360-I1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>INTERIOR ALTERATION WITHIN EXISTING TENANT SPACE STE 708 ON 7TH FLOOR IN EXISTING BUILDING: MODIFY EXISTING / ADD NEW SPRINKLER HEADS PER NEW LAYOUT NO CHANGE TO OCCUPANCY, GROUP AND USE.</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 207 KINGSBOROUGH 2 WALK BROOKLYN NY 11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>XIU</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CHEN</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2175,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>82-10 ROOSEVELT AVENUE, Queens</t>
+          <t>36-45 MAIN STREET, Queens</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2173,40 +2185,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>J &amp; G CONSTRUCTION SRVCS</t>
+          <t>MEHRAN PROPERTY MGT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Q01462609-I1</t>
+          <t>Q01453401-I1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>INSTALLATION OF AN ILLUMINATED BUSINESS ACCESSORY SIGN . NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>JIN HWAN</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>CHO</t>
         </is>
       </c>
     </row>
@@ -2221,50 +2233,50 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>372 LIVINGSTON STREET, Brooklyn</t>
+          <t>61-41 SAUNDERS STREET, Queens</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Doria Scaffolding LLC</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B01347167-P2</t>
+          <t>Q01466195-S1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY SUSPENDED SCAFFOLDS PER PLAN SUBMITTED. WORK SHALL COMPLY WITH 2022 BUILDING CODE CHAPTER 33. NO CHANGE IN USE, EGRESS AND/OR OCCUPANCY WITH THIS APPLICATION.</t>
+          <t>RESTROOM RENOVATION</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ZELJKO</t>
+          <t>KYEONGIL</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>STEVANOVIC</t>
+          <t>JANG</t>
         </is>
       </c>
     </row>
@@ -2279,17 +2291,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>86-17 NORTHERN BOULEVARD, Queens</t>
+          <t>218 LENOX AVENUE, Manhattan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MK ARCHITECTURE</t>
+          <t>AFSHARI TORK PE PC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2298,31 +2310,31 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Q01464179-I1</t>
+          <t>M00831074-P1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The scope of work consists of Interior renovation of an existing commercial space to establish new grocery store including new ceiling, wall and floor finishes, new plumbing sinks and new storefront.</t>
+          <t>INTERIOR RENOVATION AT  BASEMENT FLOOR ONLY TO CREATE AN EATING AND DRINKING ESTABLISHMENT.  INSTALLATION OF NEW MECHANICAL SYSTEM, AND PLUMBING WORK ARE FILED UNDER SEPARATE APPLICATIONS.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Mourad</t>
+          <t>SHAHRIAR</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Kicha</t>
+          <t>AFSHARI TORK</t>
         </is>
       </c>
     </row>
@@ -2337,17 +2349,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>82-57 241 STREET, Queens</t>
+          <t>403 WEST STREET, Manhattan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>STITCHT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2356,31 +2368,31 @@
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Q01312557-P1</t>
+          <t>M01443133-P1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Installation of solar system on the roof as per plan. No change in use, egress or occupancy</t>
+          <t>Plumbing work for new bathroom on fourth floor.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ayracon</t>
+          <t>JOSEPH</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Almaraz</t>
+          <t>LOMBARDI</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2407,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1211 FLATBUSH AVENUE, Brooklyn</t>
+          <t>538 54 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2414,31 +2426,31 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>108000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B01465175-I1</t>
+          <t>B01351177-P2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Interior fit-out of tenant space of existing commercial space on the first floor. Installation of new floors. No change to use, egress or occupancy.</t>
+          <t>INSTALL NEW PLUMBING FIXTURES AT CELLAR 1ST 2ND AND 3RD FLOOR. GENERAL CONSTRUCTION WORK WAS FILED UNDER DOBNOW JOB#B01351177-I1.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Hee Jun</t>
+          <t>JIE</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>ZHU</t>
         </is>
       </c>
     </row>
@@ -2453,17 +2465,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8709 3 AVENUE, Brooklyn</t>
+          <t>61-41 SAUNDERS STREET, Queens</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NEC REALTY CORP</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2472,46 +2484,46 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B01461704-I1</t>
+          <t>Q01466195-I1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Interior renovation of two existing dwelling units in a mixed use building. No change in use, egress or occupancy.</t>
+          <t>INTERIOR RENOVATION</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ashton</t>
+          <t>KYEONGIL</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Quintin</t>
+          <t>JANG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>174 BEACH  120 STREET, Queens</t>
+          <t>12-27 148 STREET, Queens</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2521,65 +2533,65 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>300 AVE Y LLC</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Q00706470-S1</t>
+          <t>Q01462113-I1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>FILING FOR CONSTRUCTION FENCE AS PER PLANS</t>
+          <t>Installation of Solar panels on existing roof structure, No change in use, egress or occupancy.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>JEFFREY</t>
+          <t>Chun</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BELL</t>
+          <t>Feng</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>100 ATLANTIC AVENUE, Staten Island</t>
+          <t>241 KINGSBOROUGH    2 WALK, Brooklyn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>NYCHA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2588,7 +2600,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2597,149 +2609,153 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>S01291782-S3</t>
+          <t>B01450005-I1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SUBSEQUENT FILING FOR MECHANICAL WORK TYPE FOR INSTALLATION OF DUCTLESS SPLIT-SYSTEM HEAT PUMPS FOR HEATING AND AIR CONDITIONING.</t>
+          <t>INSTALLATION OF NEW SIDEWALK SHED AT 241 KINGSBOROUGH 2 WALK BROOKLYN NY 11233 AS INDICATED ON PLANS. THERE WILL BE NO CHANGE IN THE USE, EGRESS, OR OCCUPANCY UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>YUNHO</t>
+          <t>WALIUR</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Full Demolition</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>40-38 189 STREET, Queens</t>
+          <t>6585 BROADWAY, Bronx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4038 EASTERN REALTY LLC</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Q01442655-I1</t>
+          <t>X01435396-I1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>FULLY DEMOLITION OF EXISTING 2 1/2 STORY HOUSE</t>
+          <t>Replacement of hot water heating boiler. No change in use, egress, or occupancy.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>XIAOHONG</t>
+          <t>Yahaira</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ZHAO</t>
+          <t>Volquez Colombo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1248 HAVEMEYER AVENUE, Bronx</t>
+          <t>111 BROADWAY, Manhattan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bronx</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CAPITAL PROPERTIES</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>101200</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X01455851-I1</t>
+          <t>M01386832-P1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>FILING FOR INTERIOR RENOVATION WORK TO CONVERT FROM ONE FAMILY TO TWO FAMILIES.</t>
+          <t>MECHANICAL MODIFICATIONS TAKING PLACE ON 20TH FLOOR AS PER PLANS FILED HEREWITH. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Akeeb</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Shekoni</t>
+          <t>Snyder</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>105 BOWERY, Manhattan</t>
+          <t>301 EAST   38 STREET, Manhattan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2749,98 +2765,906 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bowery 87 LLC</t>
+          <t>CHESTNUT HOLDINGS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>M01313825-I1</t>
+          <t>M01463437-I1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>CONVERT EXISTING INTERIM MULTIPLE DWELLING IMD)  TO OBTAIN AN AMENDED CERTIFICATE OF OCCUPANCY PER NYC LOFT BOARD REQUIREMENTS IN ACCORDANCE WITH ARTICLE 7B - NYS MULTIPLE DWELLING LAW- NO CHANGE TO EXISTING COMMERCIAL USE</t>
+          <t>FILING FOR FACADE REPIAR; REPAIR STEP CRACKS BRICK POINTING AND GRINDING AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>MICHAEL</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CETERA</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>471 GLENMORE AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>T&amp;J CONTRACTING INC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>54400</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>B01462378-I1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DUE TO NEW OWNER REPAIR THE EXISTING ROOF AS PER PLAN. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SURESH</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>WARREN</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>133 WEST  128 STREET, Manhattan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AIO BUILDING CONSULTING INC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>M01463410-I1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FILING TO REPAIR AND REPLACE STUCCO AT FRONT FACADE. NO CHANGE IN USE, EGRESS OR OCCUPANCY</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>AKM</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>RAHMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1842 HYLAN BOULEVARD, Staten Island</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1838 hylan LLC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>S01463126-I1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>PROJECT TO ADD A SECOND FLOOR RESIDENTIAL SECOND FLOOR</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Mohammad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Baalbaki</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>0</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Alteration CO</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>90-01 215 STREET, Queens</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2045 EAST   14 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>B01401287-S2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>STRUCTURAL DESIGN IN CONJUNCTION WITH GC APPLICATION B01401287-I1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>DAMIR</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>RAHMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>170-07 HILLSIDE AVENUE, Queens</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Queens</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
-      <c r="G42" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>199150</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Q01159189-P1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Extension of existing 1-family dwelling as per submitted drawing. In conjunction with BIS job#401010838. Filing to obtain a new certificate of occupancy.</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>GLEN</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>LANGER</t>
+      <c r="G46" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Q01449931-S1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>(PLUMBING WORK) APPLICATION FILING MINOR RENOVATION FOR EXISTING PROFESSIONAL OFFICE AND 1 FAMILY BUILDING IN CONNECTION GC JOB# Q01449931-I1. NO CHANGE TO USE, EGRESS, OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Mohammad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Alauddin</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>95 MADISON AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MADISON 29 HOLDING LLC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>325000</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>M01053870-B1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SUBSEQUENT FILING FOR MECHANICAL WORK IN CONJUNCTION WITH ALT-CO APPLICATION # M01053870.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>EDWIN</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DEGUZMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6918 FORT HAMILTON PARKWAY, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OM SAI REALTY LLC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>B01311638-S1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>New construction wood fence along the facade on the sidewalk</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Megalla</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>105 SOUTH    4 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>B01311619-S5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Support of Excavation during underpinning of adjacent building.  See plans submitted herewith and related PAA filed on DOBNOW job #B01311619-I1 filed in conjunction to document this work further per code and DOBNOW requirements.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Sbeglia</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2331 HERMANY AVENUE, Bronx</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bronx</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>R and V ASSETS CORP</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>83000</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X01456477-I1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Conversion of single family house to 2-family house</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Jingjun</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2331 GAR HERMANY AVENUE, Bronx</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bronx</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>R and V ASSETS CORP</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>47700</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X01456479-I1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>VERTICAL ENLARGEMENT OF EXISTING ONE-STORY DETACHED ACCESSORY GARAGE. NEW SECOND STORY CONTAINING ONE ANCILLARY DWELLING UNIT (477 SF) PER BC APPENDIX U. FIRST FLOOR REMAINS PRIVATE GARAGE, TWO SPACES. NEW CERTIFICATE OF OCCUPANCY. RELATED: X01456477-I1.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Jingjun</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Zhou</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>898 MADISON STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ATOMIC CONTRACTING INC.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>B01216883-P7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Install fire sprinkler system subsequent to GC (-I1) job.  The system is hydraulically calculated.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Gregory</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Mortman</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>No Work</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>303 BOND STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>B01451309-I1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Public Programs: Lectures, Conferences, Exhibitions, Talks, Community Board Meetings</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>HAYLEY</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>EBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Full Demolition</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>28-17 215 PLACE, Queens</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Q01393814-I1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FULLY DEMOLITION OF EXISTING 1 1/2 STORY HOUSE</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2778 MARION AVENUE, Bronx</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bronx</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>VIDA CONSTRUCTION ENTER.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>188000</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X01464167-I1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Convert one family house to a two family house.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Amauris</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>280 HANCOCK STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>B01242126-I1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Change of Use for work performed in conjunction with Job #B01387834-S2.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>MICHAEL</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>COGEN</t>
         </is>
       </c>
     </row>

--- a/data/nyc_construction_leads.xlsx
+++ b/data/nyc_construction_leads.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -493,50 +493,50 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3528 TIEMANN AVENUE, Bronx</t>
+          <t>104-21 165 STREET, Queens</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EVAN CONSTRUCTION</t>
+          <t>MAR AND MOSTAK INC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>557118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X00620397-P4</t>
+          <t>Q01460676-I1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>HEREWITH TO PROPOSE 3 STORY BUILDING WITH 3 FAMILY.</t>
+          <t>NEW BUILDING - 2 FAMILIES</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Manish</t>
+          <t>Akeeb</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Savani</t>
+          <t>Shekoni</t>
         </is>
       </c>
     </row>
@@ -551,26 +551,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3221 CRUGER AVENUE, Bronx</t>
+          <t>512 SEAGIRT AVENUE, Queens</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>NEPTUNE ASSOCIATES LLC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -579,22 +579,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X01336538-S7</t>
+          <t>Q01439794-I1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SOE SPECIFICATIONS FILED IN CONJUNCTION WITH NB APPLICATION #X01336538-I1</t>
+          <t>PROPOSED 3-STORY AND GROUND FLOOR, TWO-FAMILY MASONRY BUILDING</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DENIS</t>
+          <t>PIROOZ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PORTAEV</t>
+          <t>SOLTANIZADEH</t>
         </is>
       </c>
     </row>
@@ -609,26 +609,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>97 ALBEE AVENUE, Staten Island</t>
+          <t>506 SEAGIRT AVENUE, Queens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OUR ISLAND PROPERTY MNGNT</t>
+          <t>NEPTUNE ASSOCIATES LLC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -637,22 +637,22 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>S01173105-P3</t>
+          <t>Q01439716-I1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>PLAN AND DOCUMENTS FILED HEREWITH FOR INSTALLATION OF WATER, SANITARY FIXTURES AND ASSOCIATED PIPES FOR RESIDENCE.  AND STORMWATER DISPOSAL SYSTEMS. CORRECT HOT WATER HEATER LOCATIONS</t>
+          <t>PROPOSED 3-STORY AND GROUND FLOOR, TWO-FAMILY MASONRY BUILDING</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Giuseppe</t>
+          <t>PIROOZ</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Bonomo</t>
+          <t>SOLTANIZADEH</t>
         </is>
       </c>
     </row>
@@ -667,26 +667,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3221 CRUGER AVENUE, Bronx</t>
+          <t>508 SEAGIRT AVENUE, Queens</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>NEPTUNE ASSOCIATES LLC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -695,22 +695,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X01336538-S2</t>
+          <t>Q01439792-I1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>FOUNDATION AND EARTHWORK SPECIFICATIONS FILED IN CONJUNCTION WITH NB APPLICATION #X01336538-S2</t>
+          <t>PROPOSED 3-STORY AND GROUND FLOOR, TWO-FAMILY MASONRY BUILDING</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DENIS</t>
+          <t>PIROOZ</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PORTAEV</t>
+          <t>SOLTANIZADEH</t>
         </is>
       </c>
     </row>
@@ -725,50 +725,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50 GRANT STREET, Staten Island</t>
+          <t>84-51 129 STREET, Queens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GR1 Development LLC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>S01368840-I1</t>
+          <t>Q00770449-P7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Application is filed for the construction of new detached 10-family, 3-story with cellar residential building. All work as per plans submitted herewith.</t>
+          <t>NEW BUILDING - 2 FAMILY HOUSE AS PER PLAN.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Martarella III</t>
+          <t>ALAM</t>
         </is>
       </c>
     </row>
@@ -783,26 +783,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50 GRANT STREET, Staten Island</t>
+          <t>510 SEAGIRT AVENUE, Queens</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GR1 Development LLC</t>
+          <t>NEPTUNE ASSOCIATES LLC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -811,37 +811,37 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>S01368840-S1</t>
+          <t>Q01439793-I1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Application is filed for the plumbing work in conjunction with NB application #S01368840-I1.</t>
+          <t>PROPOSED 3-STORY AND GROUND FLOOR, TWO-FAMILY MASONRY BUILDING - DETACHED</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>PIROOZ</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Martarella III</t>
+          <t>SOLTANIZADEH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50-50 231 STREET, Queens</t>
+          <t>165-16 HORACE HARDING EXPRESSWAY, Queens</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -851,30 +851,30 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DEVELOPMENT 166 LLC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1233303</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Q01468894-I1</t>
+          <t>Q01403373-S6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>VERTICAL &amp; HORIZONTAL EXTENSION OF EXISTING ONE FAMILY + ADU. OBTAIN NEW C OF O</t>
+          <t>FILE BPP 86 LINDEAR FEET IN CONJUNCTION WITH JOB#Q01403373</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -890,65 +890,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>809 BROADWAY, Manhattan</t>
+          <t>84-49 129 STREET, Queens</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>M01224181-P2</t>
+          <t>Q00769537-P6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RENOVATION OF EXISTING SPACE WITH (14) NEW PLUMBING FIXTURES, (1) NEW ELECTRIC HOT WATER HEATER, (32) RELOCATED SPRINKLER HEADS AND (7) NEW SPRINKLER HEADS ON FIRST FLOOR AS PER PLAN FILED IN CONJUNCTION WITH GC M01200006-I1 AND MS-M01224181-I1.</t>
+          <t>NEW BUILDING - 2 FAMILY HOUSE AS PER PLAN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>HUA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>XIAO</t>
+          <t>ALAM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -957,17 +957,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8 BEACH STREET, Manhattan</t>
+          <t>90-15 QUEENS BOULEVARD, Queens</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>J &amp; G CONSTRUCTION SRVCS</t>
+          <t>MACERICH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -976,31 +976,31 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>750000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M01467689-I1</t>
+          <t>Q01426488-P1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>Space 3040 - JD - Interior alteration to existing tenant space in multi story/tenant covered mall.  Reconfiguration of space for new sales area, fitting room, stock areas, managers office. No change in use egress or occupancy.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Paulette</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Burns</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>92-06 LIBERTY AVENUE, Queens</t>
+          <t>50 BROAD STREET, Manhattan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kriya Rishi LLC</t>
+          <t>CUSHMAN &amp; WAKEFIELD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1034,31 +1034,31 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>189500</t>
+          <t>450000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Q01467882-I1</t>
+          <t>M01296795-P1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>EXISTING FIRST FLOOR COMMERCIAL RETAIL STORE TO BE RENOVATED INCLUDING NEW NON-LOAD BEARING PARTITIONS, FINISHED FLOORS AND CEILING, AND ADA COMPLIANT BATHROOM.  NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
+          <t>Install new interior partitions and finishes on second floor in the existing offices as per plans filed herewith only.  No change to zoning, egress, use, occupancy.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ashray</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Solanki</t>
+          <t>Ohrman</t>
         </is>
       </c>
     </row>
@@ -1073,50 +1073,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>64-25 136 STREET, Queens</t>
+          <t>1925 HOLLAND AVENUE, Bronx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FOUR BROTHERS GEN'L CONT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Q01458164-I1</t>
+          <t>X01341918-P5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>LEGALIZE THE ENCLOSED FRONT PORCH AND COMPLETE THE ONE-STORY WOOD-FRAMED REAR EXTENSION TO CORRECT THE VIOLATION# 39189537P.</t>
+          <t>REPLACEMENT OF EXISTING RESIDENTAL PLUMBING FIXTURES AT DWELLING UNITS AND INSTALLATION OF NAVIEN CONDENSING COMBI BOILER.NO CHANGE IN USE, EGRESS OR OCCUPANCY. GAS USAGE AND APPLIANCES COMBINATION UNIT WITH TANKLESS COIL.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>RAJESH</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>SHAH</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>90-15 QUEENS BOULEVARD, Queens</t>
+          <t>1736 BLEECKER STREET, Queens</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1141,40 +1141,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACERICH</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>324575</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Q01436186-P4</t>
+          <t>Q01431646-S1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>New storefront structure, new interior non-bearing partition walls and new ceiling framing. No change to use, egress or occupancy.</t>
+          <t>PROPOSED ALTERATION / RENOVATION OF AN EXISTING 2 STORY + CELLAR, TWO-FAMILY DWELLING. WORK PER PLANS FILED HERE WITHIN. NO CHANGE TO BULK, OCCUPANCY, NOR EGRESS.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>THOMAS</t>
+          <t>Eliza</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MORRIS</t>
+          <t>Tan</t>
         </is>
       </c>
     </row>
@@ -1189,50 +1189,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>30-40 37 STREET, Queens</t>
+          <t>1477 BEDFORD AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yan Ming Inc</t>
+          <t>GEL MANAGEMENT ENTERPRISES LLC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>362000</t>
+          <t>52725</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Q01362677-P2</t>
+          <t>B01452026-I1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PROPOSED INTERIOR RENOVATION WORK AT CELLAR, 1ST AND 2ND FLOOR. GENERAL CONSTRUCTION WORK, REMOVE &amp; INSTALL PARTITIONS, SHEETROCK, WINDOWS, &amp; FLOOR. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
+          <t>Sister new 3 x10 to Fire Damage 3 x10 wood joists at rear of the building at Exposures 2 &amp; 4 brick masonry walls 3rd Floor Ceiling</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>YUK</t>
+          <t>JACKMAN</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>PRESCOD</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2196 SCHENECTADY AVENUE, Brooklyn</t>
+          <t>113 GATES AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1257,40 +1257,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RESTORE RITE NY CORP</t>
+          <t>A+ CHOICE CONSTRUCTION INC.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>B01227508-P1</t>
+          <t>B01461280-I1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Replace plumbing fixtures on existing roughing. Install one (1) new boiler, one (1) HWH &amp; one (1) new 3" 350xl2 Wilkins lead free DCVA with one (1) new 3" combined water main from Schenectady Avenue.</t>
+          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SHAFIQUE</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ISLAM</t>
+          <t>Joseph</t>
         </is>
       </c>
     </row>
@@ -1305,50 +1305,50 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>152 WATCHOGUE ROAD, Staten Island</t>
+          <t>1 LIBERTY PLAZA, Manhattan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASM MECHANICAL CORP</t>
+          <t>Brookfield operated by CBRE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>76500</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S01446263-I1</t>
+          <t>M01381045-S3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>The scope of work as per the plans includes, replace the sheet rock on walls, false ceiling, replace sub floor, and light fixtures, repair roof as required. No change in egress, occupancy or use.</t>
+          <t>Plumbing work as shown on plans filed herewith.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>VIJAY</t>
+          <t>ARTHUR</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>METZLER</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1363,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>150 WEST   56 STREET, Manhattan</t>
+          <t>133-12 LIBERTY AVENUE, Queens</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>METROCITY CONSTRUCTION GROUP INC</t>
+          <t>RSMECHANICAL SERVICES INC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1382,31 +1382,31 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>46000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>M01461314-I1</t>
+          <t>Q01431512-I1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>INTERIOR RENOVATION OF APARTMENT#6101 ONLY, NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
+          <t>DIRECT REPLACEMENT OF ROOFTOP HVAC UNITS.  REPLACEMENT UNITS TO BE PLACED ON EXISTING DUNNAGE.  NO OTHER WORK PROPOSED.  NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Zheng</t>
+          <t>Darlyn</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Zhong</t>
+          <t>Alvarez</t>
         </is>
       </c>
     </row>
@@ -1421,50 +1421,50 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>140 WEST  106 STREET, Manhattan</t>
+          <t>120A HALL STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>GREENLINE BLDG CONSULTANTS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pending QA Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>M01468558-I1</t>
+          <t>B00454210-P3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Suspended scaffold outrigger installation for facade repair works</t>
+          <t>EXISTING 3 STORY WITH BASEMENT AND CELLAR PLUMBING WORK AS PER PLAN.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AMJAD</t>
+          <t>NOEL</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MAHMOOD</t>
+          <t>WONG</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>153-33 HILLSIDE AVENUE, Queens</t>
+          <t>13 COURTNEY LANE, Queens</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HARPS REALTY CO.INC</t>
+          <t>BREEZY POINT COOPERATIVE, INC.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1498,31 +1498,31 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Q01469290-I1</t>
+          <t>Q01464166-I1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Installation of Temp. construction Fence to facilitate facade repair work filed separately.</t>
+          <t>FEMA Flood VENTS and Metal Columns Post to replace application # 401808576 ( 34713485Z)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ABU H M</t>
+          <t>FRANK</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KAMAL</t>
+          <t>VILLANO</t>
         </is>
       </c>
     </row>
@@ -1537,46 +1537,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>363 EAST   76 STREET, Manhattan</t>
+          <t>250 GAR BEACH  140 STREET, Queens</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>129675</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>M01319654-P1</t>
+          <t>Q01450052-I1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Interior renovation of apartment 10C, including open kitchen layout, new closets, updated kitchen finishes, new flooring, doors, trim, painting, and electrical fixture/outlet updates as per plans filed. No change to use or egress.</t>
+          <t>REPLACE EXISITNG ROOF AND RENOVATE GARAGE; PROPOSED ROOF OVER</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MOHAMMED</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BETATACHE</t>
+          <t>SKVIRSKY</t>
         </is>
       </c>
     </row>
@@ -1591,50 +1595,50 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2497 GRAND AVENUE, Bronx</t>
+          <t>46 LISPENARD STREET, Manhattan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSH NY CORP DBA ELITE GROUP</t>
+          <t>MERCHANTS PROPERTIES, INC.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X01466101-I1</t>
+          <t>M01187399-P2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>Interior renovation of apartment #3E. Modification to kitchen and bathroom fixtures and appliances. No change in use, egress or occupancy. In association with GC application #M01182358-I1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Doran</t>
         </is>
       </c>
     </row>
@@ -1649,50 +1653,50 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>143-09 NEWPORT AVENUE, Queens</t>
+          <t>375 PARK AVENUE, Manhattan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>RFR REALTY LLC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>28860</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Q01469310-I1</t>
+          <t>M01460587-S3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>TEMPORARY CONSTRUCTION FENCE</t>
+          <t>MODIFICATION OF EXISTING SPRINKLER SYSTEM FOR 25TH FLOOR OFFICE SPACE. NO CHANGE TO USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NORMAN</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>LOK</t>
+          <t>Gerazounis</t>
         </is>
       </c>
     </row>
@@ -1707,17 +1711,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>170 WEST 48 STREET, Manhattan</t>
+          <t>58 WEST BURNSIDE AVENUE, Bronx</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RG</t>
+          <t>58 BURNSIDE FOOD CORP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1726,31 +1730,31 @@
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>M01468933-I1</t>
+          <t>X01379959-I1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>INSTALLATION OF AN ILLUMINATED BUSINESS ACCESSORY SIGN . NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
+          <t>NEW EXHAUST HOOD, EXHAUST DUCT AND EXHAUST FAN TO BE INSTALLED AT EXISTING MINI MARKET.  FIRESTOPPING WILL NOT BE DISTURBED.  NO OTHER WORK PROPOSED.  THERE WILL BE NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>JIN HWAN</t>
+          <t>Darlyn</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CHO</t>
+          <t>Alvarez</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1769,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>34-33 29 STREET, Queens</t>
+          <t>132-03 JAMAICA AVENUE, Queens</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1775,7 +1779,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JJL Astoria Inc</t>
+          <t>RSMECHANICAL SERVICES INC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1784,31 +1788,31 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q01376131-P3</t>
+          <t>Q01431462-I1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>PROPOSED INTERIOR RENOVATION WORK AT CELLAR, 1ST AND 2ND FLOOR. GENERAL CONSTRUCTION WORK, REMOVE &amp; INSTALL PARTITIONS, SHEETROCK, WINDOWS, &amp; FLOOR. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
+          <t>DIRECT REPLACEMENT OF ROOFTOP HVAC UNITS.  REPLACEMENT UNITS TO BE PLACED ON EXISTING DUNNAGE.  THERE IS NO OTHER WORK PROPOSED.  THERE WILL BE NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>YUK</t>
+          <t>Darlyn</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>Alvarez</t>
         </is>
       </c>
     </row>
@@ -1823,17 +1827,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>69-01 35 AVENUE, Queens</t>
+          <t>902 BROADWAY, Manhattan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akala construction inc</t>
+          <t>902 ASSOCIATES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1842,31 +1846,31 @@
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>34999.95</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Q01468232-I1</t>
+          <t>M01427398-I1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>INSTALLATION OF PIPE SCAFFOLDING AS PER PLANS. ALL EQUIPMENT SHALL COMPLY WITH CH #33 OF THE NYC CODE 2022. NO CHANGE IN USE, OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
+          <t>Propose to install new sprinkler heads and associated sprinkler branch piping.  No change in use, egress or occupancy.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MOSTAFA</t>
+          <t>Ashe</t>
         </is>
       </c>
     </row>
@@ -1881,50 +1885,50 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>922 MADISON AVENUE, Manhattan</t>
+          <t>20-08 CORNAGA AVENUE, Queens</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>BEACH CORNAGA LLC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>M01460689-I1</t>
+          <t>Q01463062-I1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>INTERIOR ALTERATION TO CORRECT VIOLATIONS. NO CHANGE IN EGRESS, USE OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>SHAFIQUE</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>ISLAM</t>
         </is>
       </c>
     </row>
@@ -1939,17 +1943,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>867 NOSTRAND AVENUE, Brooklyn</t>
+          <t>39-06 MAIN STREET, Queens</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1159 CARROLL STREET CORP</t>
+          <t>Milestone Equities</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1958,31 +1962,31 @@
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>B01414058-I1</t>
+          <t>Q01459895-I1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>APPLICATION FILED TO INSTALL KITCHEN EXHAUST SYSTEM (HOOD,DUCTWORK, MAKE-UP FAN AND EXHAUST FAN) FOR EXISTING COMMERCIALSPACE AT FIRST FLOOR AS PER PLANS. FIRE SUPPRESSION SYSTEM FILEDSEPARATELY WITH THE FDNY. NO CHANGE TO USE, EGRESS, OROCCUPANCY.</t>
+          <t>INSTALLATION OF AN ILLUMINATED BUSINESS ACCESSORY SIGN . NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SOHAIL</t>
+          <t>JIN HWAN</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>HUMAYUN</t>
+          <t>CHO</t>
         </is>
       </c>
     </row>
@@ -1997,17 +2001,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2487 GRAND AVENUE, Bronx</t>
+          <t>23-11 33 STREET, Queens</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SSH NY CORP DBA ELITE GROUP</t>
+          <t>ASA CONSTRUCTION NY CORP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2016,31 +2020,31 @@
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X01466100-I1</t>
+          <t>Q01467555-I1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>PROPOSED OF BRICK REPLACEMENT ON PARAPET WALL AND WINDOW LINTELS TO BE DONE AS NEEDED AS PER PLANS.NO CHANGE IN USE OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2059,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>57-33 228 STREET, Queens</t>
+          <t>1124 TAYLOR AVENUE, Bronx</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2070,35 +2074,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Q01467442-I1</t>
+          <t>X00942684-P1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>PLUMBING WORK FOR EXISTING (2) FAMILY DWELLING UNIT. NO CHANGE IN USE OF EGRESS &amp; OCCUPANCY.</t>
+          <t>Remove and cap all plumbing lines and gas lines and related fixtures</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CHUNG CHING</t>
+          <t>MICHAEL</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JEN</t>
+          <t>DEPASQUALE</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2117,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>136 FROST STREET, Brooklyn</t>
+          <t>92-06 LIBERTY AVENUE, Queens</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MAREK KACZOR, PE</t>
+          <t>Kriya Rishi LLC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2132,288 +2136,288 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B01426334-S1</t>
+          <t>Q01467882-S1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>shower+sink+toilet installation on new roughing</t>
+          <t>SUBSEQUENT FILING FOR THE INSTALLATION OF TOILET AND SINK IN ASSOCIATION WITH ADA COMPLIANT BATHROOM TO FIRST FLOOR RETAIL STORE ONLY. NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MAREK</t>
+          <t>Ashray</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>Solanki</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Full Demolition</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>219 DEVOE STREET, Brooklyn</t>
+          <t>250 BEACH  140 STREET, Queens</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BROOKLYN AZ INC</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B01450770-I1</t>
+          <t>Q01340867-P1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Full demolition of 2 story frame building.</t>
+          <t>PROPOSED PLUMBING</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JIANG</t>
+          <t>SKVIRSKY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2849 FULTON STREET, Brooklyn</t>
+          <t>375 PARK AVENUE, Manhattan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>RFR REALTY LLC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B01355266-S3</t>
+          <t>M01460587-S2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Subsequent Structural filing in conjunction with facade alteration of existing 1 story commercial building.</t>
+          <t>INSTALLATION OF PLUMBING FIXTURES AND RELATED PIPING ON 25TH FLOOR OFFICE SPACE AS PER PLANS. NO CHANGE TO USE, EGRESS OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>JAMES</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CHUN</t>
+          <t>Gerazounis</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>50-50 231 STREET, Queens</t>
+          <t>105 ELLIOT PLACE, Bronx</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AXIS BUILDERS INC.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Q01468894-S1</t>
+          <t>X01463383-I1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FILE SOE IN CONJUNCTION WITH JOB#Q01468894</t>
+          <t>PROPOSED OF BRICK REPLACEMENT ON PARAPET WALL TO BE DONE AS NEEDED AS PER PLANS. NO CHANGE IN USE OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>XIAOHONG</t>
+          <t>AKM</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ZHAO</t>
+          <t>RAHMAN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42-02 GAR 189 STREET, Queens</t>
+          <t>235 WEST  116 STREET, Manhattan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BO'S BAGELS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Q01141840-P1</t>
+          <t>M01466665-I1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ENLARGEMENT OF EXISTING ACCESSORY GARAGE. OBTAIN NEW C OF O.</t>
+          <t>INSTALL A NEW KITCHEN EXHAUST HOOD AT THE PARTIAL GROUND FLOOR, WITH NEW EXHAUST DUCTWORK EXTENDING TO THE ROOF AND A NEW EXHAUST FAN AT THE ROOF, AS PER PLANS. NO CHANGE IN USE, EGRESS, OR OCCUPANCY.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>XIAOHONG</t>
+          <t>FAZAL</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZHAO</t>
+          <t>BANGASH</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Full Demolition</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>37-20REAR 76 STREET, Queens</t>
+          <t>2458 EAST   27 STREET, Brooklyn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CAROLE OPEDAL</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2422,56 +2426,56 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Q01454500-I1</t>
+          <t>B01375201-S3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Full demolition of existing rear garage structure.</t>
+          <t>Installation Mitsubishi mini split units</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SHAFIQUE</t>
+          <t>OLEG</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ISLAM</t>
+          <t>RUDITSER</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>50-50 231 STREET, Queens</t>
+          <t>676 FLUSHING AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20X HOSPITALITY AT BOWERY LLC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2480,87 +2484,1401 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>166770</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Q01468894-S2</t>
+          <t>B01462363-I1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>INSTALL 8' TEMPORARY CONSTRUCTION FENCE AT THE ABOVE ADDRESS</t>
+          <t>Renovate existing commercial store on 1st floor for eating &amp; drinking establishment. Install minor partitions, finishes, flooring ceiling and plumbing fixtures. Modify existing kitchen equip, exhaust and HVAC system. No change in use, egress or occupancy.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>LAWRENCE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>MAREK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>40</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>269 COLERIDGE STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>49800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>B01355071-S3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PLUMBING WORK ONLY BEING FILED IN CONJUNCTION WITH ALTERATION DOBNOW #B01355071-I1. NEWPLUMBING PIPING AND FIXTURES PER PLANS. INSTALL NEW NAVIEN HWH AND NAVIEN TANKLESS BOILER.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Dmitriy</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Polyakov</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>530 EAST   72 STREET, Manhattan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>M01464736-I1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MINOR INTERIOR RENOVATION IN APT #4F ON THE 4TH FLOOR AS PER PLAN FILED HEREWITH. NO CHANGE IN USE, OCCUPANCY, OR EGRESS OF THE BUILDING.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>40</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>43-48 GAR AUBURNDALE LANE, Queens</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>8322 LLC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Q01467597-I1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>RENOVATIO OF ONE STORY ACCESSORY GARAGE AT REAR YARD. NO CHANGE IN USE, OCCUPANCY OR EGRESS.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>40</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>330 WEST END AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>281061</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>M01459252-I1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>APPLICATION FILED FOR MINOR NON LOAD BEARING PARTITIONS, PLUMBING WORK, AND RELATED FINISHES, AS PER PLANS.  NO CHANGE IN USE, EGRESS, OCCUPANCY OR BULK.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MARCO</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>GIARDINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5510 5 AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TITAN SERVICES USA INC.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>B01467551-I1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>INSTALLATION OF 300PSF SIDEWALK SHED AS PER PLANS. ALL EQUIPMENT SHALL COMPLY WITH CH #33 OF THE NYC CODE 2022. NO CHANGE IN USE, OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>AKM</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>RAHMAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>125 BAY   26 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>B01434817-S4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Herewith file foundation plans, filed in conjunction with Doc S-3 Structural application.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Edwin</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Cheuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>8 GRAMERCY PARK SOUTH, Manhattan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>A+ CHOICE CONSTRUCTION INC.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>M01469465-I1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Augustine</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1991 BROADWAY, Manhattan</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>M01465257-S1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>To change the fixtures of bathroom and kitchen sink on existing plumbing.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>VIJAY</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>KUMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1 LIBERTY PLAZA, Manhattan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Brookfield operated by CBRE</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>M01381045-S2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Mechanical work as shown on plans filed herewith.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ARTHUR</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>METZLER</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5618 4 AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DINE 1 LLC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2970</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>B01463142-I1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>INSTALLATION OF AN ILLUMINATED BUSINESS ACCESSORY SIGN . NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>JIN HWAN</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>330 WEST END AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>48048</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>M01459252-S1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>APPLICATION FILED FOR MINOR NON LOAD BEARING PARTITIONS, PLUMBING WORK, AND RELATED FINISHES, AS PER PLANS.  NO CHANGE IN USE, EGRESS, OCCUPANCY OR BULK.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MARCO</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>GIARDINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>40</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10 ROCKAWAY PARKWAY, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NYC SCHOOL CONSTRUCTION AUTHORITY</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>B01452554-I1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>SUPPORT OF EXCAVATION TO PROVIDE SUPPORT FOR INSTALLATION OF TWO CATCH BASIN  IN CONJUNCTION WITH DOB NOW #B01452551-I1. NO CHANGE IN USE, OCCUPANCY, OR EGRESS UNDER THIS APPLICATION</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ERFANI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1736 BLEECKER STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Q01431646-I1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>STRUCTURAL ALTERATIONS, INTERIOR RENOVATION, AND REAR CONCRETE STEPS.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MEDINA YAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2555 EAST   12 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>mz roosevelt llc</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>176710</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>B01466882-I1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>FACADE REPAIR AS PER PLAN.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ADITYA</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>DESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>40</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>32-27 54 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Provenza NYC Inc</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Q01469365-I1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Cat &amp; removal gas line (gas stove &amp; boiler). Replace plumbing fixtures on existing Routh-in</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Roxana</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Escobar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>0</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5317 7 AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>B01220503-S7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>FILE BPP APPLICATGION.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>JIE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>ZHU</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Full Demolition</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>43-14 GAR SMART STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SMART GOLDENE LLC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Q01469418-I1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>68-19 172 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Q01419940-S1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>FILE SOE IN CONJUNCTION WITH JOB#Q01419940</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>846 58 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>B01290763-S6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>INSTALLATION OF HEAVY-DUTY SIDEWALK SHED FOR NEW BUILDING OVERHEAD PROTECTION AS PER PLANS. NO CHANGE IN USE OCCUPANCY OR EGRESS UNDER THIS APPLICATION.  SIDEWALK SHED SHALL COMPLY WITH CHAPTER 33 OF THE 2022 NYC BUILDING CODE.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>KAMRUL</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>AHSAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Alteration CO</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>79-08 LANGDALE STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>260550</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Q08054146-P4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>SECOND FLOOR VERTICAL ADDITION OVER FIRST FLOOR ENVELOPE AND TWO STORY FRONT EXTENSION. NEW CELLAR ENTRANCE IN REAR YARD. PLUMBING AND FENCE WORK TYPES TO BE FILED SEPARATELY.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Solanki</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>68-19 172 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Q01419940-S5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>FILE BPP IN CONJUNCTION WITH JOB#Q01419940</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>No Work</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>365 BROADWAY, Manhattan</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>M01469372-I1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Temporary Place of Assembly (TPA) for an event accommodating up to 120 occupants for a fashion show. The event will take place on Tuesday, October 13, 2026, from 7:00 PM to 9:00 PM.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Sherif</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Abdellatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1756 SEWARD AVENUE, Bronx</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bronx</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>JS HOMES REALTY SERVICES INC.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X01110908-P2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Application to create accessory space in basement in conjunction with class A dwelling unit on first floor as shown in plansfiled herewith. No work proposed on the two dwelling units located on the second floor.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Varela</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>103-21 177 STREET, Queens</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Queens</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>York College/CUNY</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
-      <c r="G37" s="1" t="n">
-        <v>46298</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>240600</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Q01466550-I1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>APPLICATION FILING MINOR RENOVATION AND MODIFICATION INCLUDING HORIZONTAL ENLARGEMENT AS PER PLAN TO OBTAIN CERTIFICATE OF OCCUPANCY.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="G60" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Q01466550-S2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PLUMBING WORK IN CONNECTION WITH GENERAL CONSTRUCTION AS PER PLAN. NO CHANGE OF USE, EGRESS AND OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Mohammad</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>Alauddin</t>
         </is>

--- a/data/nyc_construction_leads.xlsx
+++ b/data/nyc_construction_leads.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,26 +493,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>154-34 59 AVENUE, Queens</t>
+          <t>212 WEST   29 STREET, Manhattan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Slope holdings ny</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -521,95 +521,95 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Q01453148-S5</t>
+          <t>M01438369-I1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FILE PL &amp; SP WORKTYPE IN CONJUNCTION WITH JOB#Q01453148</t>
+          <t>Development hub Job by Default; As Project is greater than Seven (7) stories, Per service notice Posted April 16, 2021 such Jobs shall be assigned to the Development Hub Unit - Subject building consists of Thirty-Five (35) stories</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KAI</t>
+          <t>Lester</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>Katz</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11 EAST   68 STREET, Manhattan</t>
+          <t>149-15 DELAWARE AVENUE, Queens</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GUMLEY HAFT, LLC</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>731836.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M00766198-P1</t>
+          <t>Q01292824-S6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9th Cycle Facade repair program. No changes to use, in egress, or occupancy.</t>
+          <t>INSTALL 18' SHARE DROP CURB INCLUDE 1'-6" SPLAYS ON BOTHSIDE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>KAI</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Larkin</t>
+          <t>HUANG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>132-29 58 AVENUE, Queens</t>
+          <t>111-38 145 STREET, Queens</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -619,55 +619,55 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1406460</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Q01195745-P5</t>
+          <t>Q01470154-I1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VERTICAL &amp; HORIZONTAL EXTENSION OF EXISTING ONE FAMILY AND CONVERTING TO TWO FAMILY HOUSE. OBTAIN NEW C OF O</t>
+          <t>NEW REAR-YARD ACCESSORY STORAGE STRUCTURE. WORK INCLUDES WOOD-FRAMED WALLS AND ROOF, ASPHALT SHINGLES, CONCRETE FOUNDATION, AND ASSOCIATED CONSTRUCTION DETAILS. FILED TO OBTAIN DOB APPROVAL FOR WORK PERFORMED WITHOUT A PERMIT.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ROBERT</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ERVOLINA</t>
+          <t>Royes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>317 WEST   93 STREET, Manhattan</t>
+          <t>83 MADISON STREET, Manhattan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -675,121 +675,125 @@
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>83 MADISON HOLDINGS LLC</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M01466193-I1</t>
+          <t>M00979759-P2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>THE PROJECT IS THE RENOVATION OF AN APARTMENT INCLUDING REPLACEMENT OF PLUMBING FIXTURES, NEW WALLS AND ALL NEW FINISHES.</t>
+          <t>Proposed construction of the 8 stories mixed use building with 18 residential units and 2 community facility units</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>JASON</t>
+          <t>ZARINA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SHANNON</t>
+          <t>KINDO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>900 THIRD AVENUE, Manhattan</t>
+          <t>112-50 38 AVENUE, Queens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PARAMOUNT GROUP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>289992</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>M01472565-I1</t>
+          <t>Q01475047-I1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Minor demolition with installation of new partitions, doors, ceilings and finishes on 1st and mezzanine floors (LL Work) as per plans.  No change to use, egress or occupancy.</t>
+          <t>PROPOSE A NEW 4 STORY 6 APARTMENTS RESIDENTIAL BUILDING. OBTAIN NEW C OF O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>XIAOHONG</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Loffredo</t>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>88-19 178 STREET, Queens</t>
+          <t>126 CLINTON AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>218 BROOKLYN LLC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -798,104 +802,104 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Q01475958-I1</t>
+          <t>B01373205-S6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Temporary construction fence 8 ft height surrounding work areas</t>
+          <t>Filing for structure of a 3 store and PH building</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>KARTIK</t>
+          <t>DENIS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHANDA</t>
+          <t>PORTAEV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94 GREENWICH AVENUE, Manhattan</t>
+          <t>122 CLINTON AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AMMAS</t>
+          <t>218 BROOKLYN LLC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>M01392227-P1</t>
+          <t>B01373202-S8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Plumbing modifications in the second-floor kitchen and bathroom and the third-floor bathroom, as shown on plans. No change in use, occupancy, or egress.</t>
+          <t>Filing for structure of a 3 store and PH building</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>DENIS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Shcherbakov</t>
+          <t>PORTAEV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>New Building</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>208 FREEMAN STREET, Brooklyn</t>
+          <t>124 CLINTON AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -905,46 +909,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>218 BROOKLYN LLC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>B00936465-P2</t>
+          <t>B01373206-S7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>INTERIOR RENOVATION OF SECOND FLOOR APARTMENT</t>
+          <t>Filing for structure of a 3 store and PH building</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ADRIAN</t>
+          <t>DENIS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>TOLBARU</t>
+          <t>PORTAEV</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -953,7 +957,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37 WEST   94 STREET, Manhattan</t>
+          <t>399 PARK AVENUE, Manhattan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>BOSTON PROPERTIES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,89 +976,89 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>52000</t>
+          <t>819776.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M01388221-P3</t>
+          <t>M01461459-I1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Herewith filing for new plumbing fixtures in conjunction with GC application.</t>
+          <t>ALTERATIONS TO EXISTING HVAC SYSTEMS AS PER PLANS FILED HEREWITH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LEMUEL</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GUIDOS</t>
+          <t>Weindel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alteration</t>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32 WEST   95 STREET, Manhattan</t>
+          <t>39-11 215 STREET, Queens</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>39-11 HGP PROPERTY GROUP LLC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pending Prof Cert QA Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>1235718</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>M01419433-S1</t>
+          <t>Q01470469-I1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Herewith filing for plumbing and gas work in conjunction with GC application M01419433-I1</t>
+          <t>VERTICAL &amp; HORIZONTAL EXTENSION OF EXISTING ONE FAMILY AND CONVERTING TO TWO FAMILY HOUSE. OBTAIN NEW C OF O.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>XIAOHONG</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
@@ -1069,50 +1073,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>300 WEST   22 STREET, Manhattan</t>
+          <t>10 8 AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Icon Realty Management, LLC</t>
+          <t>10 8TH AVENUE HOUSING CORPORATION</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending CPE/ACPE Assignment</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>M01278565-P1</t>
+          <t>B01452003-I1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>INSTALLATION OF EXTERIOR PERGOLA SYSTEM ON FIFTH FLOOR ROOF TO EXPAND THE EXISTING  ACCESSORY ROOF TERRACE FOR THE PENTHOUSE HOTEL ROOM</t>
+          <t>Install new roof deck at rear side of roof 3rd floor level asper plans. No change to use egress or occupancy.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>KARTIK</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LaPorta</t>
+          <t>CHANDA</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1131,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>454 FORT WASHINGTON AVENUE, Manhattan</t>
+          <t>154 BROOME STREET, Manhattan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALPHA SCAFFOLDING INC</t>
+          <t>YARKS NYC INC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1146,31 +1150,31 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>M01455919-I1</t>
+          <t>M01471556-I1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>INSTALLATION OF TEMPORARY HEAVY DUTY SIDEWALK SHED AS PER PLANS. NO CHANGE IN USE, EGRESS OR OCCUPANCY. SIDEWALK SHED SHALL COMPLY WITH CHAPTER #33 OF 2022 THE NYC BUILDING CODE. LIVE LOAD 300PSF.</t>
+          <t>PROPOSED INSTALLATION OF TEMPORARY FENCE AS PER PLANS. NO CHANGE IN USE OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>MOSTAFA</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1189,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>167-25 109 ROAD, Queens</t>
+          <t>150 WEST  179 STREET, Bronx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>S&amp;J CONSTRUCTION OF USA CORP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1204,31 +1208,31 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Q01473098-I1</t>
+          <t>X01445585-I1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PROPOSED TO LEGALIZE  HORIZONTAL EXTENSION IN  1ST &amp; 2ND  FLOOR  REAR SIDE OF THE BUILDING TO COMPLY ECB VIOLATION# 39204389P, 39204370P,39204350H. NO CHANGE  OCCUPANCY WITH THIS APPLICATION.</t>
+          <t>FILING TO MAINTAIN BUILDING FACADE WALLS, REPAIR CRACKED BRICK AT FACADE, STEP AND CONCRETE WALL AT CHIMNEY TO ADDRESS ECB VIOLATION# 35726341Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>KARTIK</t>
+          <t>Akeeb</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CHANDA</t>
+          <t>Shekoni</t>
         </is>
       </c>
     </row>
@@ -1243,26 +1247,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>109-47 54 AVENUE, Queens</t>
+          <t>10 AVENUE D, Manhattan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>NYC Housing Authority</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending QA Assignment</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1271,22 +1275,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Q01470777-S1</t>
+          <t>M01476061-I1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TO PROPOSE INTERIOR RENOVATION OF THE EXISTING FIRST AND SECOND FLOOR PER SCOPE OF WORK ON FLOOR PLANS.</t>
+          <t>IRA FOR THE VERTICAL CONDUIT LOCATION INSPECTION</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>GLENN</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DEFONSECA</t>
+          <t>ADELSON</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1305,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>60 MADISON AVENUE, Manhattan</t>
+          <t>118 CONKLIN AVENUE, Brooklyn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>THE MOINIAN GROUP</t>
+          <t>CANARSIE CHURCH OF CHRIST INC.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1320,31 +1324,31 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>M01473706-I1</t>
+          <t>B01426327-I1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>INTERIOR RENOVATION OF NON-LOAD BEARING PARTITIONS, CEILING, AND FINISHES ON THE 11TH FLOOR AS PER PLANS FILED HEREWITH. NO CHANGE IN USE, EGRESS OR OCCUPANCY.</t>
+          <t>INSTALL THREE (07) WALL MOUNTED AIR CONDITIONING UNIT WITH TWO NEW COMPRESSOR AS PER PLAN.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>ADITYA</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Loffredo</t>
+          <t>DESAI</t>
         </is>
       </c>
     </row>
@@ -1359,46 +1363,50 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>317 WEST   93 STREET, Manhattan</t>
+          <t>143-10 SPRINGFIELD BOULEVARD, Queens</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NYC SCHOOL CONSTRUCTION</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pending CPE/ACPE Assignment</t>
+          <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>M01466193-S1</t>
+          <t>Q01446538-I1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PLUMBING WORK RELATED TO M01466193-I1</t>
+          <t>Filing for temporary supported scaffolding in conjuction with Q01323011. No change in use, egress or occupancy.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>JASON</t>
+          <t>RAJASEKHA</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SHANNON</t>
+          <t>SAKHAMURI</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1421,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4703 ISELIN AVENUE, Bronx</t>
+          <t>157-10 46 AVENUE, Queens</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GINO LONGO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1432,56 +1440,56 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X01430996-S1</t>
+          <t>Q01475975-S1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>To replace, remove or install new plumbing fixtures as per plan.</t>
+          <t>FILE PL WORKTYPE IN CONJUNCTION WITH JOB#Q01475975</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Hal</t>
+          <t>LOUIS</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Dorfman</t>
+          <t>KONG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alteration CO</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>300 WEST   22 STREET, Manhattan</t>
+          <t>90-11 179 STREET, Queens</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Icon Realty Management, LLC</t>
+          <t>NETDT LLC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1490,46 +1498,42 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>M01248940-P1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>INSTALLATION OF EXTERIOR PERGOLA SYSTEM ON FIFTH FLOOR ROOF AND ADDING ROOF TERRACE BAR</t>
-        </is>
-      </c>
+          <t>Q01459260-S2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>MOHAMMAD</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>LaPorta</t>
+          <t>AHEAD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>No Work</t>
+          <t>Alteration</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>300 AMSTERDAM AVENUE, Manhattan</t>
+          <t>401 WEST  207 STREET, Manhattan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1537,92 +1541,2470 @@
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ROSING SCHOLARS LEARNING CENTER</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pending Plan Examiner Assignment</t>
+          <t>Pending Prof Cert QA Assignment</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>M01242509-P2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>M01337417-P1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>APPLICATION FILE FOR MINOR RENOVATION AND CREATE A NEW LAYOUT FOR A NEWLY BUILT COMMERCIAL SPACE FOR A DAY CARE AND EXISTING CO#M00666777-I1 TO REMAIN AS PER PLAN.  NO CHANGE OF USE, EGRESS, AND OCCUPANCY UNDER THIS APPLICATION.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Barak</t>
+          <t>SHEAN CHANG</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Pliskin</t>
+          <t>WANG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>34 STANLEY AVENUE, Staten Island</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>S01473003-I1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>INTERIOR RENOVATION, MINOR LAYOUT CHANGES. NO CHANGES TO USE, OCCUPANCY, EGRESS OR ZONING.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MICHAEL</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>HOUSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>41-23 UNION STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FIRST COUNTY RE LLC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Q01446181-S1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FILING PLUMBING WORK OF MEDICAL OFFICE ON 2ND FLOOR AS PER PLAN FILED HEREWITH. NO CHANGE IN USE, EGRESS OR OCCUPANCY UNDER THIS APPLICATION.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Shcherbakov</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>40</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1150 BRIGHTON BEACH AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>B01456517-P1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>INTERIOR RENOVATION OF APT 5H</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Humayun</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>48-15 164 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Q01474143-I1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TO RESOLVE ECB VIOLATIONS #35728243Y , 35728242M , 35728241K, 39203094N &amp; 30203091H,REMOVE AND CAP BATHTUB &amp; GAS LINE ,PORTABLE GAS STOVE,IN CELLAR AND PARTITION ,DOOR,WITH GENERAL CONSTRUCTION RESTORING THE USE TO ITS PRIOR LEGAL CONDITION NOCHANGE IN US</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>TONY</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ONYEAGORO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>90-11 179 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NETDT LLC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Q01459260-S1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AHEAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>46-16 160 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>30240</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q01474067-I1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Installation of Solar panels on existing roof structure, No change in use, egress or occupancy.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Chun</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Feng</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>40</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>41-23 UNION STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FIRST COUNTY RE LLC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>84525</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Q01446181-I1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>INTERIOR RENOVATION &amp; MECHANICAL WORK OF MEDICAL OFFICE ON 2ND FLOOR AS PER PLAN FILED HEREWITH. NO CHANGE IN USE, EGRESS OR OCCUPANCY UNDER THIS APPLICATION.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Shcherbakov</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>40</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1514 EAST   95 STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>B01462673-I1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>HEREWITH FILING AN APPLICATION TO CONSTRUCT A 10'-0" X 12'-0" CONCRETE STORAGE SHED IN REAR YARD. APPLICATION TO ADDRESS VIOLATION 39201272H.NO CHANGE TO USE, OCCUPANCY OR EGRESS.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>RONALD</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>VILLANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>40</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2478 BRAGG STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>B01454848-I1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Filing to Repair, replace the existing metal Porch at rear of the house in response to violation # VIO26-02100 . No change in use ,egress or occupancy</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MOSTAFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1018 MADISON AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>M01475349-I1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>REMOVAL OF STAIR FROM 5TH FLOOR TO PENTHOUSE AND PATCHING OF FLOOR.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NORMAN</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>40</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>82-27 188 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Q00565362-P4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MECHANICAL SYSTEM INSTALLATION FOR PROPOSED NEW RESIDENTIAL BUILDING AS PER PLANS HERE WITHIN. NO CHANGE TO EGRESS, USE OR OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ARSEN</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ZAVLYANOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>40</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>157-10 46 AVENUE, Queens</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>69800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Q01475975-I1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>INTERIOR RENOVATION OF EXISTING TWO STORY HOUSE. NO CHANGE IN USE, OCCUPANCY OR EGRESS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>LOUIS</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>KONG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>40</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>90-36 149 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MASTEC NETWORK SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pending QA Assignment</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Q01476086-I1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>IRA FOR THE VERTICAL CABLE TRAY LOCATION INSPECTION</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>GLENN</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ADELSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>156-71 CROSS BAY BOULEVARD, Queens</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Princess Annie LLC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Q01476080-I1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FILING HEREWITH PLANS AND APPLICATION TO INSTALL EMERGENCY FENCE INSTALLATION TO MAKE  SITE SAFE.  AS PER EMERGENCY WORK ORDER CONTROL NO: 350877</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Marmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>40</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>50-53 39 PLACE, Queens</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>13600</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Q01265558-P2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>APPLICATION IS BEING FILED FOR BASEMENT FLOOR INTERIOR RENOVATION, INSTALL FRONT ENTRANCE DOOR AND LAUNDRY AND CONVERT TWO TO THREE FIXTURE BATHROOM IN BASEMENT FOR ACCESSORY USE. NO CHANGE USE, EGRESS, OCCUPANCY AND BULK.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>KARTIK</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CHANDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>40</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>540 PARK AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LOEWS REGENCY HOTEL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pending QA Assignment</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>M01471972-I1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FISP INSPECTION (Facade Inspection Safety Program). INDUSTRIAL ROPE ACCESS TECHNIQUES AND METHODS. SEE ATTACHED PLANS. Designated Primary Site supervisor: Jesus Decola</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>JEAN</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CORTEZ NIEVES</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>40</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>251 MACON STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MNB Developers</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>172000</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>B01438655-P1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TEMPORARY SHORING OF THE EXISTING 4-STORY WOOD FRAMEY HOUSE FROM CELLAR TO ROOF TO RESOLVE EMERGENCY STATUS.NO CHANGE IN OCCUPANCY.NO CERTIFICATE OF OCCUPANCY REQUIRED.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SIMON</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JIANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>401 WEST  207 STREET, Manhattan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ROSING SCHOLARS LEARNING CENTER</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>53125</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>M01337417-P2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Propose new plumbing fixtures, all in accordance with the plans filed herewith.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SHEAN CHANG</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>40</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1150 BRIGHTON BEACH AVENUE, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>B01456518-P1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PLUMBING WORK IN APT 5H</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Humayun</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>40</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>81-15 257 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Q01399881-P3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Legalize 2 pcs bathroom and washer and dryer. And supersede 400905393</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Syed</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Naqvi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>900 FIFTH AVENUE, Manhattan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>40700</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>M01403326-P1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>RENOVATION: REPLACEMENT OF PLUMBING FIXTURES AT TENTH FLOOR LEVEL OF 900 FIFTH AVENUE, AS PER ATTACHED PLANS. NO CHANGE IN EGRESS, OCCUPANCY, USE, FLOOR AREA, VOLUME, FIRE SAFETY.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>stephan</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>thimme</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>143-10 SPRINGFIELD BOULEVARD, Queens</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NYC SCHOOL CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Q01446533-I1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Filing for sidewalk shed in conjuction with Q01323011. No change in use, egress or occupancy.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>RAJASEKHA</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>SAKHAMURI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1893 RICHMOND TERRACE, Staten Island</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NATES MANAGEMENT LLC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>S01468795-I1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Repair and reinforce existing damaged wood roof truss, including temporary shoring and installation of steel reinforcement, as shown on plans. No change in use, egress, occupancy, or floor area.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Sztukowski</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>143-10 SPRINGFIELD BOULEVARD, Queens</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NYC SCHOOL CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Q01446534-I1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Filing for temporary construction fence in conjuction with Q01323011. No change in use, egress or occupancy.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>RAJASEKHA</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>SAKHAMURI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>83-25 98 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Q01474675-I1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>INTERIOR RENOVATION OF APT 2C. NEW FLOORING &amp; TILE FINISHES THROUGHOUT THE BATHROOM &amp; KITCHEN; SKIM COAT OF WALLS AND CEILING.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>JOMO</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CHARLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alteration</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>41-20 162 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ZKW ENTERPRISES INC.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Q01474939-I1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>INSTALLATION OF 300PSF SIDEWALK SHED AS PER PLANS. ALL EQUIPMENT SHALL COMPLY WITH CH #33 OF THE NYC CODE 2022. NO CHANGE IN USE, OCCUPANCY OR EGRESS UNDER THIS APPLICATION.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MOSTAFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pending CPE/ACPE Assignment</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>984818</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Q01450074-I1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>VERTICAL AND HORIZONTAL EXTENSION OF EXISTING ONE FAMILY + ADU. OBTAIN NEW C OF O.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>0</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Alteration CO</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>444 AVENUE T, Brooklyn</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>146-42 184 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>135-01 226TH STREET LLC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Q01279512-S2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>MECHANICAL WORK IN CONJUNCTION WITH ALT-CO JOB# Q0179512-I1.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Syed</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Naqvi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>533 QUINCY STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DR 18 CAPITAL LLC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Pending Plan Examiner Assignment</t>
         </is>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G49" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>B01168403-P1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Change of use from A 6 to A 2 family.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>JEFFREY</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>BELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>116 EAST   82 STREET, Manhattan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>89 2ND PLACE LLC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>39000</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>M01373124-S4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Install new sprinkler system as per plans.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>DARIUSZ</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>LUCZAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Q01450074-S5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>FILE PL WORKTYPE IN CONJUNCTION WITH JOB#Q01450074</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Q01450074-S4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>INSTALL 8' TEMPORARY CONSTRUCTION FENCE AT THE ABOVE ADDRESS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Q01450074-S1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>FILE SOE IN CONJUNCTION WITH JOB#Q01450074</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>39-11 215 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>39-11 HGP PROPERTY GROUP LLC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Q01470469-S1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>INSTALL SOE IN CONJUNCTION WITH JOB#Q01470469</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>68505</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Q01450074-S2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>FILE FOUNDATION AND EARTH WORK IN CONJUNCTION WITH JOB#Q01450074</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>65-55 173 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Q01450074-S3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>FILE STRUCTURE IN CONJUNCTION WITH JOB#Q01450074</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>KAI</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>HUANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ALT-CO - New Building with Existing Elements to Remain</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>53-50 61 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>96000</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Q01250828-P2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>PLUMBING WORK TYPE HAS BEEN FILED IN CONJUNCTION WITH CONSTRUCTION  #Q01250828-I1 AS PER PLANS SUBMITTED.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SERDAR</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CEYLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>69-44 172 STREET, Queens</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>31500</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Q01397973-S3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PLUMBING WORK IN CONJUNCTION WITH ALT-CO APPLICATION Q01397973-I1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>MARK</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>AMINOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>503 WEST   57 STREET, Manhattan</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>B01252761-P3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>STRUCTURAL WORK IN CONJUNCTION TO ALT1 APPLICATION B01252761-I1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>DAMIR</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>RAHMAN</t>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>M00892071-P4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>CHANGE OF USE GROUP ON GROUND FLOOR TO RESOLVE VIOLATION #35153852P AND CONVERT COMMERCIAL 2ND AND 3RD FLOORS TO RESIDENTIAL OCCUPANCY.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>MIRO</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Stracar</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>136 FRANKLIN STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PACIFIC HOLDING ENTERPRISES LLC</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pending Prof Cert QA Assignment</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>B00786304-S3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Installation of a temporary supported scaffold and heavy-duty sidewalk shed per plan submitted. Work shall comply with 2022 building codes chapter 33. No change in use, egress and/or occupancy with this application.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Amal Hassan</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>533A QUINCY STREET, Brooklyn</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Brooklyn</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DR 18 CAPITAL LLC</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>B01168404-P1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Change of use from 4 to 2 family</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>JEFFREY</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>BELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Alteration CO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>108-59 51 AVENUE, Queens</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AL &amp; JD REALTY LLC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pending Plan Examiner Assignment</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>79350</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Q01347322-P1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>CONVERT EXISTING FOUR FAMILY DWELLING UNITS TO THREE FAMILY. NO CHANGE IN THE BUILDING BULK. OBTAIN NEW C OF O.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>XIAOHONG</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ZHAO</t>
         </is>
       </c>
     </row>
